--- a/Labs/3.3.4/Data.xlsx
+++ b/Labs/3.3.4/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mihso\Documents\Study-data\Labs\3.3.4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BEBD541-E738-4CD8-B25D-23122B8AF459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CE2F1E-3893-47B8-9A46-7C6885E4B4B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{3181CAC9-620A-41E8-8380-2415784D5272}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="13">
   <si>
     <t>I, A</t>
   </si>
@@ -80,7 +80,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -148,12 +148,12 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3811,7 +3811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B884705-C8E8-4E0C-81CE-950DE55B86FF}">
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -3875,11 +3875,11 @@
         <v>8.7837190124949417E-4</v>
       </c>
       <c r="J2" s="4">
-        <f>B2</f>
+        <f t="shared" ref="J2:J7" si="0">B2</f>
         <v>0.24</v>
       </c>
       <c r="K2" s="4">
-        <f>F2</f>
+        <f t="shared" ref="K2:K7" si="1">F2</f>
         <v>233.93333333333331</v>
       </c>
     </row>
@@ -3900,23 +3900,23 @@
         <v>448.7</v>
       </c>
       <c r="F3" s="4">
-        <f t="shared" ref="F3:F7" si="0">AVERAGE(C3:E3)</f>
+        <f t="shared" ref="F3:F7" si="2">AVERAGE(C3:E3)</f>
         <v>447.56666666666666</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" ref="G3:I7" si="1">_xlfn.STDEV.P(C3:E3)</f>
+        <f t="shared" ref="G3:G7" si="3">_xlfn.STDEV.P(C3:E3)</f>
         <v>0.80553639823963463</v>
       </c>
       <c r="H3" s="5">
-        <f t="shared" ref="H3:H7" si="2">G3/F3</f>
+        <f t="shared" ref="H3:H7" si="4">G3/F3</f>
         <v>1.7998132082512131E-3</v>
       </c>
       <c r="J3" s="4">
-        <f>B3</f>
+        <f t="shared" si="0"/>
         <v>0.47</v>
       </c>
       <c r="K3" s="4">
-        <f>F3</f>
+        <f t="shared" si="1"/>
         <v>447.56666666666666</v>
       </c>
     </row>
@@ -3937,23 +3937,23 @@
         <v>686.4</v>
       </c>
       <c r="F4" s="4">
+        <f t="shared" si="2"/>
+        <v>684.63333333333333</v>
+      </c>
+      <c r="G4" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2657891697364911</v>
+      </c>
+      <c r="H4" s="5">
+        <f t="shared" si="4"/>
+        <v>1.8488570569207233E-3</v>
+      </c>
+      <c r="J4" s="4">
         <f t="shared" si="0"/>
-        <v>684.63333333333333</v>
-      </c>
-      <c r="G4" s="4">
+        <v>0.71</v>
+      </c>
+      <c r="K4" s="4">
         <f t="shared" si="1"/>
-        <v>1.2657891697364911</v>
-      </c>
-      <c r="H4" s="5">
-        <f t="shared" si="2"/>
-        <v>1.8488570569207233E-3</v>
-      </c>
-      <c r="J4" s="4">
-        <f>B4</f>
-        <v>0.71</v>
-      </c>
-      <c r="K4" s="4">
-        <f>F4</f>
         <v>684.63333333333333</v>
       </c>
     </row>
@@ -3974,23 +3974,23 @@
         <v>868.8</v>
       </c>
       <c r="F5" s="4">
+        <f t="shared" si="2"/>
+        <v>868.63333333333321</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" si="3"/>
+        <v>0.46427960923947281</v>
+      </c>
+      <c r="H5" s="5">
+        <f t="shared" si="4"/>
+        <v>5.3449435040424365E-4</v>
+      </c>
+      <c r="J5" s="4">
         <f t="shared" si="0"/>
-        <v>868.63333333333321</v>
-      </c>
-      <c r="G5" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="K5" s="4">
         <f t="shared" si="1"/>
-        <v>0.46427960923947281</v>
-      </c>
-      <c r="H5" s="5">
-        <f t="shared" si="2"/>
-        <v>5.3449435040424365E-4</v>
-      </c>
-      <c r="J5" s="4">
-        <f>B5</f>
-        <v>0.96</v>
-      </c>
-      <c r="K5" s="4">
-        <f>F5</f>
         <v>868.63333333333321</v>
       </c>
     </row>
@@ -4011,23 +4011,23 @@
         <v>986.2</v>
       </c>
       <c r="F6" s="4">
+        <f t="shared" si="2"/>
+        <v>984.86666666666679</v>
+      </c>
+      <c r="G6" s="4">
+        <f t="shared" si="3"/>
+        <v>1.1953614051361121</v>
+      </c>
+      <c r="H6" s="5">
+        <f t="shared" si="4"/>
+        <v>1.2137291732919298E-3</v>
+      </c>
+      <c r="J6" s="4">
         <f t="shared" si="0"/>
-        <v>984.86666666666679</v>
-      </c>
-      <c r="G6" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="K6" s="4">
         <f t="shared" si="1"/>
-        <v>1.1953614051361121</v>
-      </c>
-      <c r="H6" s="5">
-        <f t="shared" si="2"/>
-        <v>1.2137291732919298E-3</v>
-      </c>
-      <c r="J6" s="4">
-        <f>B6</f>
-        <v>1.2</v>
-      </c>
-      <c r="K6" s="4">
-        <f>F6</f>
         <v>984.86666666666679</v>
       </c>
     </row>
@@ -4048,23 +4048,23 @@
         <v>1044.5999999999999</v>
       </c>
       <c r="F7" s="4">
+        <f t="shared" si="2"/>
+        <v>1044.3333333333333</v>
+      </c>
+      <c r="G7" s="4">
+        <f t="shared" si="3"/>
+        <v>1.4007934259634076</v>
+      </c>
+      <c r="H7" s="5">
+        <f t="shared" si="4"/>
+        <v>1.3413278895276805E-3</v>
+      </c>
+      <c r="J7" s="4">
         <f t="shared" si="0"/>
-        <v>1044.3333333333333</v>
-      </c>
-      <c r="G7" s="4">
+        <v>1.36</v>
+      </c>
+      <c r="K7" s="4">
         <f t="shared" si="1"/>
-        <v>1.4007934259634076</v>
-      </c>
-      <c r="H7" s="5">
-        <f t="shared" si="2"/>
-        <v>1.3413278895276805E-3</v>
-      </c>
-      <c r="J7" s="4">
-        <f>B7</f>
-        <v>1.36</v>
-      </c>
-      <c r="K7" s="4">
-        <f>F7</f>
         <v>1044.3333333333333</v>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="7">
+      <c r="A10" s="9">
         <v>0.14000000000000001</v>
       </c>
       <c r="B10" s="10">
@@ -4095,81 +4095,81 @@
       <c r="C10" s="6">
         <v>0.24</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="7">
         <v>0</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="8">
         <f>D10-$B$10</f>
         <v>1.6E-2</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
+      <c r="A11" s="9"/>
       <c r="B11" s="10"/>
       <c r="C11" s="6">
         <v>0.47</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="E11" s="9">
-        <f t="shared" ref="E11:E15" si="3">D11-$B$10</f>
+      <c r="E11" s="8">
+        <f t="shared" ref="E11:E15" si="5">D11-$B$10</f>
         <v>2.8999999999999998E-2</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
+      <c r="A12" s="9"/>
       <c r="B12" s="10"/>
       <c r="C12" s="6">
         <v>0.71</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="7">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="E12" s="9">
-        <f t="shared" si="3"/>
+      <c r="E12" s="8">
+        <f t="shared" si="5"/>
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
+      <c r="A13" s="9"/>
       <c r="B13" s="10"/>
       <c r="C13" s="6">
         <v>0.96</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="E13" s="9">
-        <f t="shared" si="3"/>
+      <c r="E13" s="8">
+        <f t="shared" si="5"/>
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
+      <c r="A14" s="9"/>
       <c r="B14" s="10"/>
       <c r="C14" s="6">
         <v>1.2</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="7">
         <v>3.9E-2</v>
       </c>
-      <c r="E14" s="9">
-        <f t="shared" si="3"/>
+      <c r="E14" s="8">
+        <f t="shared" si="5"/>
         <v>5.5E-2</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
+      <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="6">
         <v>1.36</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="7">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="E15" s="9">
-        <f t="shared" si="3"/>
+      <c r="E15" s="8">
+        <f t="shared" si="5"/>
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
@@ -4191,7 +4191,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="7">
+      <c r="A17" s="9">
         <v>0.31</v>
       </c>
       <c r="B17" s="10">
@@ -4200,82 +4200,82 @@
       <c r="C17" s="6">
         <v>0.24</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <v>2E-3</v>
       </c>
-      <c r="E17" s="9">
-        <f>D17-$B$10</f>
-        <v>1.8000000000000002E-2</v>
+      <c r="E17" s="8">
+        <f>D17-$B$17</f>
+        <v>3.6000000000000004E-2</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
+      <c r="A18" s="9"/>
       <c r="B18" s="10"/>
       <c r="C18" s="6">
         <v>0.47</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <v>0.03</v>
       </c>
-      <c r="E18" s="9">
-        <f t="shared" ref="E18:E22" si="4">D18-$B$10</f>
-        <v>4.5999999999999999E-2</v>
+      <c r="E18" s="8">
+        <f t="shared" ref="E18:E22" si="6">D18-$B$17</f>
+        <v>6.4000000000000001E-2</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
+      <c r="A19" s="9"/>
       <c r="B19" s="10"/>
       <c r="C19" s="6">
         <v>0.71</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="E19" s="9">
-        <f t="shared" si="4"/>
-        <v>7.2000000000000008E-2</v>
+      <c r="E19" s="8">
+        <f t="shared" si="6"/>
+        <v>0.09</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="7"/>
+      <c r="A20" s="9"/>
       <c r="B20" s="10"/>
       <c r="C20" s="6">
         <v>0.96</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="7">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E20" s="9">
-        <f t="shared" si="4"/>
-        <v>9.0999999999999998E-2</v>
+      <c r="E20" s="8">
+        <f t="shared" si="6"/>
+        <v>0.109</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
+      <c r="A21" s="9"/>
       <c r="B21" s="10"/>
       <c r="C21" s="6">
         <v>1.2</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="7">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="E21" s="9">
-        <f t="shared" si="4"/>
-        <v>0.10299999999999999</v>
+      <c r="E21" s="8">
+        <f t="shared" si="6"/>
+        <v>0.121</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="7"/>
+      <c r="A22" s="9"/>
       <c r="B22" s="10"/>
       <c r="C22" s="6">
         <v>1.36</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="7">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="E22" s="9">
-        <f t="shared" si="4"/>
-        <v>0.109</v>
+      <c r="E22" s="8">
+        <f t="shared" si="6"/>
+        <v>0.127</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -4296,7 +4296,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="7">
+      <c r="A24" s="9">
         <v>0.48</v>
       </c>
       <c r="B24" s="10">
@@ -4305,82 +4305,82 @@
       <c r="C24" s="6">
         <v>0.24</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="7">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="E24" s="9">
-        <f>D24-$B$10</f>
-        <v>0.02</v>
+      <c r="E24" s="8">
+        <f>D24-$B$24</f>
+        <v>5.5999999999999994E-2</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="7"/>
+      <c r="A25" s="9"/>
       <c r="B25" s="10"/>
       <c r="C25" s="6">
         <v>0.47</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="7">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="E25" s="9">
-        <f t="shared" ref="E25:E29" si="5">D25-$B$10</f>
-        <v>6.2E-2</v>
+      <c r="E25" s="8">
+        <f t="shared" ref="E25:E29" si="7">D25-$B$24</f>
+        <v>9.8000000000000004E-2</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="7"/>
+      <c r="A26" s="9"/>
       <c r="B26" s="10"/>
       <c r="C26" s="6">
         <v>0.71</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="7">
         <v>0.09</v>
       </c>
-      <c r="E26" s="9">
-        <f t="shared" si="5"/>
-        <v>0.106</v>
+      <c r="E26" s="8">
+        <f t="shared" si="7"/>
+        <v>0.14199999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="7"/>
+      <c r="A27" s="9"/>
       <c r="B27" s="10"/>
       <c r="C27" s="6">
         <v>0.96</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="7">
         <v>0.11799999999999999</v>
       </c>
-      <c r="E27" s="9">
-        <f t="shared" si="5"/>
-        <v>0.13400000000000001</v>
+      <c r="E27" s="8">
+        <f t="shared" si="7"/>
+        <v>0.16999999999999998</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="7"/>
+      <c r="A28" s="9"/>
       <c r="B28" s="10"/>
       <c r="C28" s="6">
         <v>1.2</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="7">
         <v>0.13600000000000001</v>
       </c>
-      <c r="E28" s="9">
-        <f t="shared" si="5"/>
-        <v>0.15200000000000002</v>
+      <c r="E28" s="8">
+        <f t="shared" si="7"/>
+        <v>0.188</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="7"/>
+      <c r="A29" s="9"/>
       <c r="B29" s="10"/>
       <c r="C29" s="6">
         <v>1.35</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="7">
         <v>0.14399999999999999</v>
       </c>
-      <c r="E29" s="9">
-        <f t="shared" si="5"/>
-        <v>0.15999999999999998</v>
+      <c r="E29" s="8">
+        <f t="shared" si="7"/>
+        <v>0.19599999999999998</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -4401,7 +4401,7 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="7">
+      <c r="A31" s="9">
         <v>0.65</v>
       </c>
       <c r="B31" s="10">
@@ -4410,82 +4410,82 @@
       <c r="C31" s="6">
         <v>0.24</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="7">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="E31" s="9">
-        <f>D31-$B$10</f>
-        <v>2.1000000000000001E-2</v>
+      <c r="E31" s="8">
+        <f>D31-$B$31</f>
+        <v>7.5000000000000011E-2</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="7"/>
+      <c r="A32" s="9"/>
       <c r="B32" s="10"/>
       <c r="C32" s="6">
         <v>0.47</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="7">
         <v>6.2E-2</v>
       </c>
-      <c r="E32" s="9">
-        <f t="shared" ref="E32:E36" si="6">D32-$B$10</f>
-        <v>7.8E-2</v>
+      <c r="E32" s="8">
+        <f t="shared" ref="E32:E36" si="8">D32-$B$31</f>
+        <v>0.13200000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="7"/>
+      <c r="A33" s="9"/>
       <c r="B33" s="10"/>
       <c r="C33" s="6">
         <v>0.71</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="7">
         <v>0.122</v>
       </c>
-      <c r="E33" s="9">
-        <f t="shared" si="6"/>
-        <v>0.13800000000000001</v>
+      <c r="E33" s="8">
+        <f t="shared" si="8"/>
+        <v>0.192</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="7"/>
+      <c r="A34" s="9"/>
       <c r="B34" s="10"/>
       <c r="C34" s="6">
         <v>0.96</v>
       </c>
-      <c r="D34" s="8">
+      <c r="D34" s="7">
         <v>0.16</v>
       </c>
-      <c r="E34" s="9">
-        <f t="shared" si="6"/>
-        <v>0.17599999999999999</v>
+      <c r="E34" s="8">
+        <f t="shared" si="8"/>
+        <v>0.23</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="7"/>
+      <c r="A35" s="9"/>
       <c r="B35" s="10"/>
       <c r="C35" s="6">
         <v>1.2</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D35" s="7">
         <v>0.185</v>
       </c>
-      <c r="E35" s="9">
-        <f t="shared" si="6"/>
-        <v>0.20100000000000001</v>
+      <c r="E35" s="8">
+        <f t="shared" si="8"/>
+        <v>0.255</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="7"/>
+      <c r="A36" s="9"/>
       <c r="B36" s="10"/>
       <c r="C36" s="6">
         <v>1.35</v>
       </c>
-      <c r="D36" s="8">
+      <c r="D36" s="7">
         <v>0.19500000000000001</v>
       </c>
-      <c r="E36" s="9">
-        <f t="shared" si="6"/>
-        <v>0.21100000000000002</v>
+      <c r="E36" s="8">
+        <f t="shared" si="8"/>
+        <v>0.26500000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -4506,7 +4506,7 @@
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="7">
+      <c r="A38" s="9">
         <v>0.82</v>
       </c>
       <c r="B38" s="10">
@@ -4515,82 +4515,82 @@
       <c r="C38" s="6">
         <v>0.24</v>
       </c>
-      <c r="D38" s="8">
+      <c r="D38" s="7">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="E38" s="9">
-        <f>D38-$B$10</f>
-        <v>2.1000000000000001E-2</v>
+      <c r="E38" s="8">
+        <f>D38-$B$38</f>
+        <v>9.5000000000000001E-2</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="7"/>
+      <c r="A39" s="9"/>
       <c r="B39" s="10"/>
       <c r="C39" s="6">
         <v>0.47</v>
       </c>
-      <c r="D39" s="8">
+      <c r="D39" s="7">
         <v>0.08</v>
       </c>
-      <c r="E39" s="9">
-        <f t="shared" ref="E39:E43" si="7">D39-$B$10</f>
-        <v>9.6000000000000002E-2</v>
+      <c r="E39" s="8">
+        <f t="shared" ref="E39:E43" si="9">D39-$B$38</f>
+        <v>0.16999999999999998</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="7"/>
+      <c r="A40" s="9"/>
       <c r="B40" s="10"/>
       <c r="C40" s="6">
         <v>0.71</v>
       </c>
-      <c r="D40" s="8">
+      <c r="D40" s="7">
         <v>0.155</v>
       </c>
-      <c r="E40" s="9">
-        <f t="shared" si="7"/>
-        <v>0.17099999999999999</v>
+      <c r="E40" s="8">
+        <f t="shared" si="9"/>
+        <v>0.245</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="7"/>
+      <c r="A41" s="9"/>
       <c r="B41" s="10"/>
       <c r="C41" s="6">
         <v>0.96</v>
       </c>
-      <c r="D41" s="8">
+      <c r="D41" s="7">
         <v>0.20200000000000001</v>
       </c>
-      <c r="E41" s="9">
-        <f t="shared" si="7"/>
-        <v>0.21800000000000003</v>
+      <c r="E41" s="8">
+        <f t="shared" si="9"/>
+        <v>0.29200000000000004</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="7"/>
+      <c r="A42" s="9"/>
       <c r="B42" s="10"/>
       <c r="C42" s="6">
         <v>1.2</v>
       </c>
-      <c r="D42" s="8">
+      <c r="D42" s="7">
         <v>0.23400000000000001</v>
       </c>
-      <c r="E42" s="9">
-        <f t="shared" si="7"/>
-        <v>0.25</v>
+      <c r="E42" s="8">
+        <f t="shared" si="9"/>
+        <v>0.32400000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="7"/>
+      <c r="A43" s="9"/>
       <c r="B43" s="10"/>
       <c r="C43" s="6">
         <v>1.34</v>
       </c>
-      <c r="D43" s="8">
+      <c r="D43" s="7">
         <v>0.248</v>
       </c>
-      <c r="E43" s="9">
-        <f t="shared" si="7"/>
-        <v>0.26400000000000001</v>
+      <c r="E43" s="8">
+        <f t="shared" si="9"/>
+        <v>0.33799999999999997</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -4611,7 +4611,7 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="7">
+      <c r="A45" s="9">
         <v>0.99</v>
       </c>
       <c r="B45" s="10">
@@ -4620,86 +4620,197 @@
       <c r="C45" s="6">
         <v>0.24</v>
       </c>
-      <c r="D45" s="8">
+      <c r="D45" s="7">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="E45" s="9">
-        <f>D45-$B$10</f>
-        <v>2.3E-2</v>
+      <c r="E45" s="8">
+        <f>D45-$B$45</f>
+        <v>0.114</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="7"/>
+      <c r="A46" s="9"/>
       <c r="B46" s="10"/>
       <c r="C46" s="6">
         <v>0.47</v>
       </c>
-      <c r="D46" s="8">
+      <c r="D46" s="7">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="E46" s="9">
-        <f t="shared" ref="E46:E50" si="8">D46-$B$10</f>
-        <v>0.113</v>
+      <c r="E46" s="8">
+        <f t="shared" ref="E46:E50" si="10">D46-$B$45</f>
+        <v>0.20400000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="7"/>
+      <c r="A47" s="9"/>
       <c r="B47" s="10"/>
       <c r="C47" s="6">
         <v>0.71</v>
       </c>
-      <c r="D47" s="8">
+      <c r="D47" s="7">
         <v>0.186</v>
       </c>
-      <c r="E47" s="9">
-        <f t="shared" si="8"/>
-        <v>0.20200000000000001</v>
+      <c r="E47" s="8">
+        <f t="shared" si="10"/>
+        <v>0.29299999999999998</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="7"/>
+      <c r="A48" s="9"/>
       <c r="B48" s="10"/>
       <c r="C48" s="6">
         <v>0.96</v>
       </c>
-      <c r="D48" s="8">
+      <c r="D48" s="7">
         <v>0.24299999999999999</v>
       </c>
-      <c r="E48" s="9">
-        <f t="shared" si="8"/>
-        <v>0.25900000000000001</v>
+      <c r="E48" s="8">
+        <f t="shared" si="10"/>
+        <v>0.35</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="7"/>
+      <c r="A49" s="9"/>
       <c r="B49" s="10"/>
       <c r="C49" s="6">
         <v>1.2</v>
       </c>
-      <c r="D49" s="8">
+      <c r="D49" s="7">
         <v>0.28199999999999997</v>
       </c>
-      <c r="E49" s="9">
-        <f t="shared" si="8"/>
-        <v>0.29799999999999999</v>
+      <c r="E49" s="8">
+        <f t="shared" si="10"/>
+        <v>0.38899999999999996</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="7"/>
+      <c r="A50" s="9"/>
       <c r="B50" s="10"/>
       <c r="C50" s="6">
         <v>1.34</v>
       </c>
-      <c r="D50" s="8">
+      <c r="D50" s="7">
         <v>0.29699999999999999</v>
       </c>
-      <c r="E50" s="9">
-        <f t="shared" si="8"/>
-        <v>0.313</v>
+      <c r="E50" s="8">
+        <f t="shared" si="10"/>
+        <v>0.40399999999999997</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="9">
+        <v>1</v>
+      </c>
+      <c r="B52" s="10">
+        <v>-0.107</v>
+      </c>
+      <c r="C52" s="6">
+        <v>0.24</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-0.224</v>
+      </c>
+      <c r="E52" s="8">
+        <f>D52-$B$52</f>
+        <v>-0.11700000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="9"/>
+      <c r="B53" s="10"/>
+      <c r="C53" s="6">
+        <v>0.47</v>
+      </c>
+      <c r="D53" s="7">
+        <v>-0.31900000000000001</v>
+      </c>
+      <c r="E53" s="8">
+        <f t="shared" ref="E53:E57" si="11">D53-$B$52</f>
+        <v>-0.21200000000000002</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="9"/>
+      <c r="B54" s="10"/>
+      <c r="C54" s="6">
+        <v>0.71</v>
+      </c>
+      <c r="D54" s="7">
+        <v>-0.41299999999999998</v>
+      </c>
+      <c r="E54" s="8">
+        <f t="shared" si="11"/>
+        <v>-0.30599999999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="9"/>
+      <c r="B55" s="10"/>
+      <c r="C55" s="6">
+        <v>0.96</v>
+      </c>
+      <c r="D55" s="7">
+        <v>-0.47499999999999998</v>
+      </c>
+      <c r="E55" s="8">
+        <f t="shared" si="11"/>
+        <v>-0.36799999999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="9"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="D56" s="7">
+        <v>-0.51300000000000001</v>
+      </c>
+      <c r="E56" s="8">
+        <f t="shared" si="11"/>
+        <v>-0.40600000000000003</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="9"/>
+      <c r="B57" s="10"/>
+      <c r="C57" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="D57" s="7">
+        <v>-0.53</v>
+      </c>
+      <c r="E57" s="8">
+        <f t="shared" si="11"/>
+        <v>-0.42300000000000004</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
+    <mergeCell ref="A10:A15"/>
+    <mergeCell ref="B10:B15"/>
+    <mergeCell ref="A17:A22"/>
+    <mergeCell ref="B17:B22"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="B52:B57"/>
     <mergeCell ref="A45:A50"/>
     <mergeCell ref="B45:B50"/>
     <mergeCell ref="A24:A29"/>
@@ -4708,10 +4819,6 @@
     <mergeCell ref="B31:B36"/>
     <mergeCell ref="A38:A43"/>
     <mergeCell ref="B38:B43"/>
-    <mergeCell ref="A10:A15"/>
-    <mergeCell ref="B10:B15"/>
-    <mergeCell ref="A17:A22"/>
-    <mergeCell ref="B17:B22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
